--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N68_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N68_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>68.28732938274611</v>
+        <v>11.09669102469624</v>
       </c>
       <c r="D2" t="n">
-        <v>67.73390806887032</v>
+        <v>11.00676006119143</v>
       </c>
       <c r="E2" t="n">
-        <v>2.688026334558501</v>
+        <v>0.4368042793657567</v>
       </c>
       <c r="F2" t="n">
-        <v>12.0274600784886</v>
+        <v>1.954462262754398</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>73.66338205186311</v>
+        <v>11.97029958342776</v>
       </c>
       <c r="D3" t="n">
-        <v>91.78882822584752</v>
+        <v>14.91568458670022</v>
       </c>
       <c r="E3" t="n">
-        <v>2.688026334558501</v>
+        <v>0.4368042793657567</v>
       </c>
       <c r="F3" t="n">
-        <v>12.0274600784886</v>
+        <v>1.954462262754398</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
